--- a/data/trans_orig/P36B10-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B10-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2007</t>
+          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2007 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35214</t>
+          <t>35734</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64059</t>
+          <t>62923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20470</t>
+          <t>19650</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41855</t>
+          <t>42104</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61896</t>
+          <t>60701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96670</t>
+          <t>98059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59409</t>
+          <t>58821</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92270</t>
+          <t>92308</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40132</t>
+          <t>40393</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66344</t>
+          <t>65951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104978</t>
+          <t>103450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148523</t>
+          <t>145179</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>124563</t>
+          <t>124116</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>165524</t>
+          <t>163478</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>111514</t>
+          <t>112409</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145069</t>
+          <t>145583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>245630</t>
+          <t>247068</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>300582</t>
+          <t>301416</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118564</t>
+          <t>117451</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>156866</t>
+          <t>158290</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62284</t>
+          <t>60437</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91434</t>
+          <t>91138</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>187016</t>
+          <t>187327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236817</t>
+          <t>239319</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55999</t>
+          <t>54049</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84941</t>
+          <t>85780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13866</t>
+          <t>13887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32797</t>
+          <t>32803</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75685</t>
+          <t>76316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110358</t>
+          <t>113353</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23810</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20656</t>
+          <t>21238</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42751</t>
+          <t>43190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32992</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59653</t>
+          <t>60704</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38055</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66345</t>
+          <t>66453</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51138</t>
+          <t>51933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80362</t>
+          <t>79860</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96762</t>
+          <t>95764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136131</t>
+          <t>135765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126052</t>
+          <t>126613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>164158</t>
+          <t>164742</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>153348</t>
+          <t>151176</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>190481</t>
+          <t>190195</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>288286</t>
+          <t>286571</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>343361</t>
+          <t>342812</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89360</t>
+          <t>90208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125615</t>
+          <t>125526</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56908</t>
+          <t>58994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87414</t>
+          <t>88119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>153916</t>
+          <t>155710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202230</t>
+          <t>204428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38513</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64866</t>
+          <t>65579</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23267</t>
+          <t>23272</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44969</t>
+          <t>44886</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>69372</t>
+          <t>68923</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103201</t>
+          <t>103024</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26408</t>
+          <t>26288</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19938</t>
+          <t>19983</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>20243</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41707</t>
+          <t>39882</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66863</t>
+          <t>66390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101400</t>
+          <t>102189</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21360</t>
+          <t>19898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42130</t>
+          <t>40639</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93538</t>
+          <t>92909</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>134352</t>
+          <t>134288</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>139129</t>
+          <t>138616</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>181319</t>
+          <t>180929</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55959</t>
+          <t>55866</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80929</t>
+          <t>80621</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>203355</t>
+          <t>200124</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>253920</t>
+          <t>252149</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>145542</t>
+          <t>144909</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>190016</t>
+          <t>191850</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30055</t>
+          <t>30671</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51634</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>184118</t>
+          <t>186943</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>238525</t>
+          <t>233419</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>97846</t>
+          <t>97427</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134850</t>
+          <t>136101</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26095</t>
+          <t>25153</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110889</t>
+          <t>111630</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>153071</t>
+          <t>151982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46766</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81310</t>
+          <t>77149</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35062</t>
+          <t>35763</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62461</t>
+          <t>62441</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87324</t>
+          <t>86933</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131110</t>
+          <t>129073</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106574</t>
+          <t>105597</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>148825</t>
+          <t>147804</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>108629</t>
+          <t>109619</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>149521</t>
+          <t>151566</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>227321</t>
+          <t>226043</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>287270</t>
+          <t>284071</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>353945</t>
+          <t>353213</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>415010</t>
+          <t>418653</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>251920</t>
+          <t>250953</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>303770</t>
+          <t>301912</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>619445</t>
+          <t>619975</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>704041</t>
+          <t>705154</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>357410</t>
+          <t>355964</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>422348</t>
+          <t>419812</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>175080</t>
+          <t>175311</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>224015</t>
+          <t>221545</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>548198</t>
+          <t>547193</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>628273</t>
+          <t>623571</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>244464</t>
+          <t>246162</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>302146</t>
+          <t>304331</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48736</t>
+          <t>48457</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>78780</t>
+          <t>78924</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>303179</t>
+          <t>303054</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>368972</t>
+          <t>368751</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30286</t>
+          <t>31543</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30950</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>57689</t>
+          <t>57947</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>47755</t>
+          <t>48814</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>79506</t>
+          <t>81557</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23682</t>
+          <t>24210</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46090</t>
+          <t>46740</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74886</t>
+          <t>73133</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>110502</t>
+          <t>110452</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>104259</t>
+          <t>103900</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>147642</t>
+          <t>147082</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>91254</t>
+          <t>89629</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>127110</t>
+          <t>126895</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>201082</t>
+          <t>203012</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>249284</t>
+          <t>248017</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>302605</t>
+          <t>306517</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>364317</t>
+          <t>364049</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>88416</t>
+          <t>89309</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>126013</t>
+          <t>124327</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>147110</t>
+          <t>146723</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>192831</t>
+          <t>188901</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>247451</t>
+          <t>246813</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>304198</t>
+          <t>303628</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>64165</t>
+          <t>64897</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>96578</t>
+          <t>96906</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28091</t>
+          <t>28044</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>52773</t>
+          <t>51752</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>98833</t>
+          <t>100762</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>139222</t>
+          <t>139978</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18721</t>
+          <t>18680</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>93608</t>
+          <t>95947</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>135498</t>
+          <t>138068</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>101845</t>
+          <t>104458</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>148487</t>
+          <t>147060</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>22216</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>183573</t>
+          <t>185336</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>234263</t>
+          <t>236866</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>196554</t>
+          <t>197724</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>252181</t>
+          <t>249215</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>64772</t>
+          <t>63083</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>95586</t>
+          <t>93009</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>484115</t>
+          <t>483319</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>553090</t>
+          <t>553956</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>558472</t>
+          <t>559236</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>632112</t>
+          <t>635765</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>77870</t>
+          <t>78525</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>109631</t>
+          <t>109486</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>231168</t>
+          <t>227714</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>288442</t>
+          <t>283913</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>320363</t>
+          <t>314755</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>384859</t>
+          <t>379426</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>85057</t>
+          <t>85788</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>117567</t>
+          <t>117772</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>128076</t>
+          <t>127138</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>171857</t>
+          <t>172062</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>225368</t>
+          <t>225250</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>279705</t>
+          <t>280779</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>148336</t>
+          <t>149277</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>200972</t>
+          <t>199793</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>244951</t>
+          <t>246356</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>313278</t>
+          <t>310412</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>407962</t>
+          <t>404525</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>491571</t>
+          <t>489477</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>346900</t>
+          <t>349938</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>420666</t>
+          <t>421694</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>529299</t>
+          <t>529081</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>618903</t>
+          <t>624889</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>896739</t>
+          <t>899000</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1016587</t>
+          <t>1012783</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>965497</t>
+          <t>964185</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1075751</t>
+          <t>1074127</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1325667</t>
+          <t>1330915</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1442274</t>
+          <t>1442534</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2325077</t>
+          <t>2326291</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2482746</t>
+          <t>2477127</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>947048</t>
+          <t>939250</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1057912</t>
+          <t>1052200</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>762000</t>
+          <t>759801</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>860506</t>
+          <t>858356</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1735997</t>
+          <t>1744689</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1882386</t>
+          <t>1889693</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>644005</t>
+          <t>644243</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>740673</t>
+          <t>737455</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>289830</t>
+          <t>290607</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>356534</t>
+          <t>356711</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>954457</t>
+          <t>955497</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1075479</t>
+          <t>1069911</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2012</t>
+          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2012 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>18540</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39940</t>
+          <t>40962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20988</t>
+          <t>21366</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45407</t>
+          <t>46970</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44463</t>
+          <t>44439</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77560</t>
+          <t>77603</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73149</t>
+          <t>73113</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>107586</t>
+          <t>109231</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73192</t>
+          <t>74498</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>107285</t>
+          <t>107719</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155472</t>
+          <t>156179</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>205304</t>
+          <t>204177</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>115051</t>
+          <t>114113</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>156761</t>
+          <t>157269</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>92549</t>
+          <t>91402</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>129243</t>
+          <t>127441</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>217392</t>
+          <t>217742</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>273275</t>
+          <t>273507</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,54%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104381</t>
+          <t>106682</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145605</t>
+          <t>144681</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40188</t>
+          <t>42791</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69669</t>
+          <t>71266</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>156156</t>
+          <t>154836</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>206322</t>
+          <t>202432</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44005</t>
+          <t>43861</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75485</t>
+          <t>76295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16685</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36153</t>
+          <t>36152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68983</t>
+          <t>67553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104212</t>
+          <t>102852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45158</t>
+          <t>44160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27583</t>
+          <t>27389</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52839</t>
+          <t>54213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52984</t>
+          <t>53826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86795</t>
+          <t>90119</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67122</t>
+          <t>68666</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104491</t>
+          <t>106109</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58712</t>
+          <t>58287</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92104</t>
+          <t>90264</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135185</t>
+          <t>136231</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>182981</t>
+          <t>184910</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>116486</t>
+          <t>116579</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156767</t>
+          <t>157780</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>109063</t>
+          <t>108504</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>147366</t>
+          <t>146616</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>235561</t>
+          <t>234589</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>289352</t>
+          <t>291628</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95311</t>
+          <t>95985</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131616</t>
+          <t>133290</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46997</t>
+          <t>48149</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76894</t>
+          <t>77264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>153716</t>
+          <t>151803</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>199992</t>
+          <t>202070</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37346</t>
+          <t>37907</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67592</t>
+          <t>67497</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26879</t>
+          <t>26428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51880</t>
+          <t>50313</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71602</t>
+          <t>70117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109136</t>
+          <t>109330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34447</t>
+          <t>35525</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62759</t>
+          <t>64005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21556</t>
+          <t>21111</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42697</t>
+          <t>41991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64182</t>
+          <t>61110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97236</t>
+          <t>95835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103787</t>
+          <t>105084</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146284</t>
+          <t>148885</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58855</t>
+          <t>58842</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>88898</t>
+          <t>87569</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173656</t>
+          <t>172316</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>224948</t>
+          <t>221776</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>173944</t>
+          <t>173034</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>222139</t>
+          <t>222767</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73767</t>
+          <t>71968</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>104225</t>
+          <t>103311</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>254155</t>
+          <t>256718</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>311071</t>
+          <t>314759</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>145657</t>
+          <t>146465</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>192140</t>
+          <t>191108</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31755</t>
+          <t>31239</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56244</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>185252</t>
+          <t>184679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>238640</t>
+          <t>236839</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71030</t>
+          <t>71540</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>109539</t>
+          <t>108521</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35968</t>
+          <t>36015</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94048</t>
+          <t>92254</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>133723</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78476</t>
+          <t>77335</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>116511</t>
+          <t>116439</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64215</t>
+          <t>65253</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100732</t>
+          <t>100767</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>151346</t>
+          <t>150776</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>201459</t>
+          <t>205056</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>234249</t>
+          <t>236584</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>294609</t>
+          <t>296013</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>183284</t>
+          <t>186055</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>232978</t>
+          <t>237953</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>434249</t>
+          <t>433429</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>511982</t>
+          <t>514774</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>317786</t>
+          <t>317058</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>382229</t>
+          <t>380657</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>203572</t>
+          <t>205208</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>256714</t>
+          <t>258392</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>539867</t>
+          <t>538197</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>620342</t>
+          <t>622270</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>271526</t>
+          <t>268606</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>330426</t>
+          <t>327759</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>150240</t>
+          <t>149060</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>196739</t>
+          <t>196836</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>429175</t>
+          <t>428338</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>507246</t>
+          <t>509250</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>125669</t>
+          <t>123179</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>170760</t>
+          <t>170213</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56104</t>
+          <t>55258</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>88690</t>
+          <t>88713</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>191473</t>
+          <t>190998</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>246565</t>
+          <t>246430</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>13970</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34284</t>
+          <t>34713</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>68788</t>
+          <t>70056</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>106164</t>
+          <t>105104</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>90923</t>
+          <t>90667</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>130892</t>
+          <t>131618</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>91364</t>
+          <t>90473</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>127100</t>
+          <t>128792</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>193732</t>
+          <t>193331</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>245204</t>
+          <t>243997</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>299422</t>
+          <t>294889</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>361011</t>
+          <t>359605</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>119942</t>
+          <t>120313</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>161056</t>
+          <t>161219</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>200137</t>
+          <t>199639</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>252083</t>
+          <t>248693</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>334489</t>
+          <t>334427</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>398764</t>
+          <t>400378</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>127782</t>
+          <t>126765</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>167066</t>
+          <t>169169</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>147211</t>
+          <t>149033</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>197473</t>
+          <t>194547</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>284691</t>
+          <t>286688</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>344754</t>
+          <t>347626</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>68916</t>
+          <t>69103</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>103057</t>
+          <t>103122</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>41469</t>
+          <t>40655</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>70013</t>
+          <t>70109</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>116856</t>
+          <t>118634</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>162137</t>
+          <t>164014</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>23609</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>104610</t>
+          <t>103615</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>148072</t>
+          <t>148162</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>117747</t>
+          <t>120062</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>162981</t>
+          <t>167736</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>36840</t>
+          <t>38089</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>264223</t>
+          <t>264698</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>323222</t>
+          <t>324989</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>284783</t>
+          <t>287416</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>351167</t>
+          <t>349092</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>59616</t>
+          <t>60193</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>87968</t>
+          <t>88495</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>324119</t>
+          <t>327123</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>388298</t>
+          <t>389397</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>395171</t>
+          <t>394651</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>467818</t>
+          <t>466458</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>65276</t>
+          <t>65065</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>94901</t>
+          <t>94455</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>172803</t>
+          <t>175660</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>224985</t>
+          <t>227772</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,47 +9539,47 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
+          <t>20,73%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>279250</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>250826</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>309851</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
           <t>20,48%</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>279250</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>249251</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>308928</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>20,48%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>55955</t>
+          <t>57292</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>86724</t>
+          <t>85204</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>105659</t>
+          <t>105863</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>148803</t>
+          <t>147768</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>172377</t>
+          <t>173121</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>225106</t>
+          <t>223431</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>209260</t>
+          <t>207975</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>273918</t>
+          <t>272484</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>354796</t>
+          <t>353736</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>436224</t>
+          <t>433287</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>586210</t>
+          <t>583044</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>692212</t>
+          <t>682455</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>647529</t>
+          <t>648927</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>752672</t>
+          <t>750619</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>902908</t>
+          <t>903035</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1015220</t>
+          <t>1010189</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1587074</t>
+          <t>1582543</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1731073</t>
+          <t>1737171</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>982894</t>
+          <t>975731</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1097775</t>
+          <t>1086088</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1078568</t>
+          <t>1075191</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1195652</t>
+          <t>1190642</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2086985</t>
+          <t>2089381</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2246229</t>
+          <t>2259421</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>875560</t>
+          <t>876757</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>980751</t>
+          <t>986526</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>649901</t>
+          <t>653664</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>750952</t>
+          <t>756235</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1561876</t>
+          <t>1560581</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1698425</t>
+          <t>1707674</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>457240</t>
+          <t>456034</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>543422</t>
+          <t>547055</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>301441</t>
+          <t>303357</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>376534</t>
+          <t>373381</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>780856</t>
+          <t>782878</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>893236</t>
+          <t>896331</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2016</t>
+          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2016 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27820</t>
+          <t>27393</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52561</t>
+          <t>53021</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23402</t>
+          <t>22670</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45319</t>
+          <t>44030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56774</t>
+          <t>56300</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90071</t>
+          <t>87770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55306</t>
+          <t>56315</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86723</t>
+          <t>88037</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68579</t>
+          <t>71110</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99176</t>
+          <t>102090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131371</t>
+          <t>131123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>179961</t>
+          <t>178411</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>178669</t>
+          <t>178740</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>223099</t>
+          <t>220788</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>107498</t>
+          <t>107005</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145799</t>
+          <t>143925</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>296924</t>
+          <t>299376</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>350888</t>
+          <t>353843</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82046</t>
+          <t>81536</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116452</t>
+          <t>116750</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68728</t>
+          <t>67816</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101561</t>
+          <t>100430</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>158445</t>
+          <t>159076</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>209311</t>
+          <t>208476</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29783</t>
+          <t>31269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11465</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28804</t>
+          <t>28914</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27435</t>
+          <t>27822</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53061</t>
+          <t>53775</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13968</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34281</t>
+          <t>34047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16394</t>
+          <t>16300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37229</t>
+          <t>37906</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34471</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63432</t>
+          <t>64156</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60783</t>
+          <t>59565</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93278</t>
+          <t>91102</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68984</t>
+          <t>70480</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103854</t>
+          <t>103974</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136873</t>
+          <t>139606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185203</t>
+          <t>189394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126344</t>
+          <t>123975</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>163916</t>
+          <t>163299</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>130963</t>
+          <t>134084</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>170170</t>
+          <t>170156</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>266701</t>
+          <t>267822</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>321846</t>
+          <t>322067</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,23%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85403</t>
+          <t>86005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120758</t>
+          <t>122205</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59538</t>
+          <t>60076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90736</t>
+          <t>91893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>153688</t>
+          <t>153816</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200584</t>
+          <t>201895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>21104</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42401</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22660</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45363</t>
+          <t>44737</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49109</t>
+          <t>49262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79529</t>
+          <t>80248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>15146</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34123</t>
+          <t>33590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11795</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29183</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30335</t>
+          <t>31530</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57002</t>
+          <t>57513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73061</t>
+          <t>74331</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107668</t>
+          <t>109885</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31478</t>
+          <t>31819</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54557</t>
+          <t>55714</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>112543</t>
+          <t>111588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>155981</t>
+          <t>154059</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>194826</t>
+          <t>195866</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>240109</t>
+          <t>242232</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41877</t>
+          <t>40032</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65910</t>
+          <t>65800</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>245858</t>
+          <t>243351</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>295401</t>
+          <t>297490</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110042</t>
+          <t>110566</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>151439</t>
+          <t>152141</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30835</t>
+          <t>31426</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54573</t>
+          <t>54246</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>151498</t>
+          <t>150350</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>195405</t>
+          <t>194237</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44607</t>
+          <t>45545</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73475</t>
+          <t>74254</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17739</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53893</t>
+          <t>54153</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84893</t>
+          <t>86908</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54743</t>
+          <t>55528</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89125</t>
+          <t>88912</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53675</t>
+          <t>54519</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85317</t>
+          <t>86024</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>117680</t>
+          <t>119690</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>164281</t>
+          <t>165056</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152540</t>
+          <t>147845</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>196883</t>
+          <t>199758</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>134520</t>
+          <t>136644</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>179020</t>
+          <t>181730</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>295198</t>
+          <t>298361</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>364021</t>
+          <t>364153</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>388753</t>
+          <t>388043</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>455007</t>
+          <t>455143</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>293279</t>
+          <t>294522</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>348780</t>
+          <t>351055</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>704610</t>
+          <t>699130</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>790546</t>
+          <t>785003</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>302278</t>
+          <t>305332</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>367086</t>
+          <t>368599</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>176848</t>
+          <t>177366</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>225021</t>
+          <t>224322</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>495851</t>
+          <t>495251</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>574917</t>
+          <t>574042</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>124977</t>
+          <t>123215</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>168330</t>
+          <t>171927</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58882</t>
+          <t>58394</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91683</t>
+          <t>93549</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,47 +13296,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>219698</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>191436</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>247192</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>11,16%</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>219698</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>192283</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>246912</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36870</t>
+          <t>36351</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65303</t>
+          <t>64769</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>49444</t>
+          <t>48001</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>83990</t>
+          <t>80289</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93488</t>
+          <t>91374</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>136173</t>
+          <t>132182</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>92044</t>
+          <t>93070</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>130072</t>
+          <t>131865</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>147761</t>
+          <t>147940</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>195500</t>
+          <t>194166</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>248412</t>
+          <t>251115</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>308022</t>
+          <t>309926</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>199308</t>
+          <t>198463</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>247077</t>
+          <t>245941</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>264682</t>
+          <t>265060</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>318076</t>
+          <t>319580</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>477015</t>
+          <t>478602</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>548900</t>
+          <t>548741</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>133521</t>
+          <t>132092</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>176867</t>
+          <t>177426</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>142862</t>
+          <t>141361</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>188027</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>287473</t>
+          <t>285614</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>348417</t>
+          <t>348803</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>64482</t>
+          <t>65413</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>99637</t>
+          <t>99552</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>37287</t>
+          <t>36543</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>65631</t>
+          <t>64913</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>110763</t>
+          <t>112093</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>154414</t>
+          <t>155319</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22234</t>
+          <t>23352</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>94514</t>
+          <t>94653</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>136594</t>
+          <t>133342</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>104521</t>
+          <t>106474</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>148889</t>
+          <t>149477</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24406</t>
+          <t>23254</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>45452</t>
+          <t>45259</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>224383</t>
+          <t>221661</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>281229</t>
+          <t>280776</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>254475</t>
+          <t>256266</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>316564</t>
+          <t>320648</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>83960</t>
+          <t>83826</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>116276</t>
+          <t>117427</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>352975</t>
+          <t>360532</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>418711</t>
+          <t>421085</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>450035</t>
+          <t>450825</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>525177</t>
+          <t>522839</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>85348</t>
+          <t>84406</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>117276</t>
+          <t>117098</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>220635</t>
+          <t>221704</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>276978</t>
+          <t>278458</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>316598</t>
+          <t>318892</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>384030</t>
+          <t>384621</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>30957</t>
+          <t>30439</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>55115</t>
+          <t>55012</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>61153</t>
+          <t>61012</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>95634</t>
+          <t>95277</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>99042</t>
+          <t>99518</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>140497</t>
+          <t>141655</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>187700</t>
+          <t>189538</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>246416</t>
+          <t>249118</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>289053</t>
+          <t>287188</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>362239</t>
+          <t>358390</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>497160</t>
+          <t>497742</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>587939</t>
+          <t>587928</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>511314</t>
+          <t>510911</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>598219</t>
+          <t>601161</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>740440</t>
+          <t>742395</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>841535</t>
+          <t>843877</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1280734</t>
+          <t>1275266</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1415664</t>
+          <t>1414937</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1253171</t>
+          <t>1245251</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1370168</t>
+          <t>1359887</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1273588</t>
+          <t>1273591</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1393120</t>
+          <t>1387385</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15121,7 +15121,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2549322</t>
+          <t>2557248</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2716093</t>
+          <t>2718690</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>872779</t>
+          <t>870015</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>980189</t>
+          <t>971240</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>765070</t>
+          <t>764120</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>864716</t>
+          <t>862645</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1666478</t>
+          <t>1663646</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1814335</t>
+          <t>1808147</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>338146</t>
+          <t>338861</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>414197</t>
+          <t>416924</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>232161</t>
+          <t>227381</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>292621</t>
+          <t>293944</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>592030</t>
+          <t>587704</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>686867</t>
+          <t>686528</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">

--- a/data/trans_orig/P36B10-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B10-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35734</t>
+          <t>35833</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62923</t>
+          <t>63835</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19650</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42104</t>
+          <t>40900</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60701</t>
+          <t>59687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98059</t>
+          <t>94712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58821</t>
+          <t>56891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92308</t>
+          <t>90676</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40393</t>
+          <t>39900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65951</t>
+          <t>66523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103450</t>
+          <t>107670</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145179</t>
+          <t>148048</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>124116</t>
+          <t>125588</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>163478</t>
+          <t>165659</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>112409</t>
+          <t>112207</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145583</t>
+          <t>145747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>247068</t>
+          <t>246882</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>301416</t>
+          <t>300842</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117451</t>
+          <t>118162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>158290</t>
+          <t>159202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60437</t>
+          <t>60883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91138</t>
+          <t>90855</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>187327</t>
+          <t>187127</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>239319</t>
+          <t>237048</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54049</t>
+          <t>55646</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85780</t>
+          <t>86786</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>14258</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32803</t>
+          <t>32540</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76316</t>
+          <t>75155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>113353</t>
+          <t>112280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23608</t>
+          <t>24697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>20723</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43190</t>
+          <t>41784</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>33432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60704</t>
+          <t>60724</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>39252</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66453</t>
+          <t>67304</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51933</t>
+          <t>51645</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79860</t>
+          <t>81381</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95764</t>
+          <t>95972</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135765</t>
+          <t>135753</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126613</t>
+          <t>125958</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>164742</t>
+          <t>164109</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>151176</t>
+          <t>151806</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>190195</t>
+          <t>190340</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>286571</t>
+          <t>289888</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>342812</t>
+          <t>342715</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,45%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90208</t>
+          <t>89858</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125526</t>
+          <t>125598</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58994</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88119</t>
+          <t>88113</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155710</t>
+          <t>157171</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>204428</t>
+          <t>203585</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65579</t>
+          <t>63788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23272</t>
+          <t>23316</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44886</t>
+          <t>44328</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68923</t>
+          <t>67132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103024</t>
+          <t>102668</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26288</t>
+          <t>26242</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>19403</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20243</t>
+          <t>20090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39882</t>
+          <t>40554</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66390</t>
+          <t>67657</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102189</t>
+          <t>100885</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19898</t>
+          <t>21323</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40639</t>
+          <t>42210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92909</t>
+          <t>95601</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>134288</t>
+          <t>134655</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>138616</t>
+          <t>137700</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180929</t>
+          <t>180052</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55866</t>
+          <t>57203</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80621</t>
+          <t>81446</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>200124</t>
+          <t>202621</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>252149</t>
+          <t>253439</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>144909</t>
+          <t>147060</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>191850</t>
+          <t>191876</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>30181</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>52518</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>186943</t>
+          <t>185539</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>233419</t>
+          <t>235774</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>97427</t>
+          <t>95835</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>136101</t>
+          <t>134044</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9309</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25153</t>
+          <t>24803</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111630</t>
+          <t>112799</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>151982</t>
+          <t>153551</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46294</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77149</t>
+          <t>77794</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62441</t>
+          <t>60601</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86933</t>
+          <t>89040</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129073</t>
+          <t>129021</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>105597</t>
+          <t>107736</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>147804</t>
+          <t>147307</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>109619</t>
+          <t>109077</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>151566</t>
+          <t>149183</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>226043</t>
+          <t>225945</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>284071</t>
+          <t>286611</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>353213</t>
+          <t>353204</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>418653</t>
+          <t>420009</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>250953</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>301912</t>
+          <t>304692</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>619975</t>
+          <t>619168</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705154</t>
+          <t>701583</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>355964</t>
+          <t>357002</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>419812</t>
+          <t>424569</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>175311</t>
+          <t>172117</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>221545</t>
+          <t>219400</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>547193</t>
+          <t>545093</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>623571</t>
+          <t>626634</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>246162</t>
+          <t>247368</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>304331</t>
+          <t>303619</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48457</t>
+          <t>48619</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>78924</t>
+          <t>78944</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>303054</t>
+          <t>306636</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>368751</t>
+          <t>369599</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12398</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31543</t>
+          <t>30869</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32280</t>
+          <t>32198</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>57947</t>
+          <t>59808</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>48814</t>
+          <t>48689</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>81557</t>
+          <t>82136</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24210</t>
+          <t>23660</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46740</t>
+          <t>46438</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>73133</t>
+          <t>74973</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>110452</t>
+          <t>110615</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>103900</t>
+          <t>104348</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>147082</t>
+          <t>144153</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>89629</t>
+          <t>90887</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>126895</t>
+          <t>128231</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>203012</t>
+          <t>201297</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>248017</t>
+          <t>247417</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>306517</t>
+          <t>305805</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>364049</t>
+          <t>364588</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,89%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>89309</t>
+          <t>89313</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>124327</t>
+          <t>124964</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>146723</t>
+          <t>146291</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>188901</t>
+          <t>189724</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>246813</t>
+          <t>244835</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>303628</t>
+          <t>303956</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>64897</t>
+          <t>65252</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>96906</t>
+          <t>95260</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28044</t>
+          <t>28526</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51752</t>
+          <t>51940</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>100762</t>
+          <t>100490</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>139978</t>
+          <t>141734</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18680</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>95947</t>
+          <t>89958</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>138068</t>
+          <t>134463</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>104458</t>
+          <t>103788</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>147060</t>
+          <t>146763</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22216</t>
+          <t>21389</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>185336</t>
+          <t>184471</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>236866</t>
+          <t>238052</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>197724</t>
+          <t>197052</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>249215</t>
+          <t>252178</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>63083</t>
+          <t>63503</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>93009</t>
+          <t>95010</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>483319</t>
+          <t>480897</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>553956</t>
+          <t>549396</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>559236</t>
+          <t>557324</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>635765</t>
+          <t>636619</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>78525</t>
+          <t>79080</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>109486</t>
+          <t>110501</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>227714</t>
+          <t>228634</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>283913</t>
+          <t>284857</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>314755</t>
+          <t>320203</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>379426</t>
+          <t>383566</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>85788</t>
+          <t>85775</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>117772</t>
+          <t>117774</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>127138</t>
+          <t>129282</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>172062</t>
+          <t>173831</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>225250</t>
+          <t>222388</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>280779</t>
+          <t>279207</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>149277</t>
+          <t>147328</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>199793</t>
+          <t>202055</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>246356</t>
+          <t>244713</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>310412</t>
+          <t>311070</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>404525</t>
+          <t>404321</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>489477</t>
+          <t>487334</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>349938</t>
+          <t>343667</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>421694</t>
+          <t>420105</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>529081</t>
+          <t>529727</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>624889</t>
+          <t>616742</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>899000</t>
+          <t>899239</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1012783</t>
+          <t>1013497</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>964185</t>
+          <t>969347</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1074127</t>
+          <t>1072608</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1330915</t>
+          <t>1333715</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1442534</t>
+          <t>1443667</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2326291</t>
+          <t>2331841</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2477127</t>
+          <t>2487602</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>939250</t>
+          <t>943697</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1052200</t>
+          <t>1051029</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>759801</t>
+          <t>759354</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>858356</t>
+          <t>858639</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1744689</t>
+          <t>1741644</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1889693</t>
+          <t>1883776</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>644243</t>
+          <t>642126</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>737455</t>
+          <t>737092</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>290607</t>
+          <t>290536</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>356711</t>
+          <t>356545</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>955497</t>
+          <t>953671</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1069911</t>
+          <t>1068232</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40962</t>
+          <t>40279</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>21357</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46970</t>
+          <t>44421</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44439</t>
+          <t>44629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77603</t>
+          <t>78719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73113</t>
+          <t>73501</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109231</t>
+          <t>108859</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74498</t>
+          <t>72249</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>107719</t>
+          <t>106299</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156179</t>
+          <t>158206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>204177</t>
+          <t>204822</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114113</t>
+          <t>115198</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>157269</t>
+          <t>156747</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>91402</t>
+          <t>92553</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>127441</t>
+          <t>129695</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>217742</t>
+          <t>217015</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>273507</t>
+          <t>270915</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106682</t>
+          <t>102319</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144681</t>
+          <t>145113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42791</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71266</t>
+          <t>70075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154836</t>
+          <t>158195</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>202432</t>
+          <t>206968</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43861</t>
+          <t>45065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76295</t>
+          <t>75559</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>17962</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36152</t>
+          <t>38259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67553</t>
+          <t>67913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102852</t>
+          <t>104976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>20729</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44160</t>
+          <t>45198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27389</t>
+          <t>28018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54213</t>
+          <t>52414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53826</t>
+          <t>54247</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90119</t>
+          <t>90251</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68666</t>
+          <t>67162</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106109</t>
+          <t>102716</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58287</t>
+          <t>59982</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90264</t>
+          <t>91067</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136231</t>
+          <t>135740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>184910</t>
+          <t>186871</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>116579</t>
+          <t>117663</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>157780</t>
+          <t>158132</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108504</t>
+          <t>108889</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>146616</t>
+          <t>145015</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>234589</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>291628</t>
+          <t>292768</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95985</t>
+          <t>96271</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133290</t>
+          <t>132978</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48149</t>
+          <t>47985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77264</t>
+          <t>76916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151803</t>
+          <t>150324</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202070</t>
+          <t>197836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37907</t>
+          <t>38680</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67497</t>
+          <t>68216</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26428</t>
+          <t>25657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50313</t>
+          <t>51496</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70117</t>
+          <t>69281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109330</t>
+          <t>109108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35525</t>
+          <t>35254</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64005</t>
+          <t>63319</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21111</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41991</t>
+          <t>42868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61110</t>
+          <t>62848</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95835</t>
+          <t>97788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105084</t>
+          <t>107142</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>148885</t>
+          <t>147300</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58842</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87569</t>
+          <t>88495</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>172316</t>
+          <t>173232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>221776</t>
+          <t>225125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>173034</t>
+          <t>174157</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>222767</t>
+          <t>221894</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71968</t>
+          <t>72692</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103311</t>
+          <t>104850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>256718</t>
+          <t>257994</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>314759</t>
+          <t>317944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,9%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>146465</t>
+          <t>145391</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>191108</t>
+          <t>192757</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31239</t>
+          <t>30781</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>53518</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>184679</t>
+          <t>185040</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>236839</t>
+          <t>238733</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71540</t>
+          <t>69956</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108521</t>
+          <t>106720</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16099</t>
+          <t>16579</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36015</t>
+          <t>35650</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92254</t>
+          <t>92622</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133723</t>
+          <t>136831</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77335</t>
+          <t>77838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>116439</t>
+          <t>114891</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65253</t>
+          <t>66275</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100767</t>
+          <t>101667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>150776</t>
+          <t>152040</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>205056</t>
+          <t>204970</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>236584</t>
+          <t>235432</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>296013</t>
+          <t>294556</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>186055</t>
+          <t>182394</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>237953</t>
+          <t>236499</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>433429</t>
+          <t>434347</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>514774</t>
+          <t>511221</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>317058</t>
+          <t>317422</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>380657</t>
+          <t>379821</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>205208</t>
+          <t>208238</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>258392</t>
+          <t>258394</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>538197</t>
+          <t>536107</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>622270</t>
+          <t>621116</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>268606</t>
+          <t>272293</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>327759</t>
+          <t>330026</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>149060</t>
+          <t>148913</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>196836</t>
+          <t>196710</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>428338</t>
+          <t>431102</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>509250</t>
+          <t>516354</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123179</t>
+          <t>124931</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>170213</t>
+          <t>170774</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55258</t>
+          <t>53720</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>88713</t>
+          <t>88964</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>190998</t>
+          <t>191621</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>246430</t>
+          <t>248892</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>15143</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34713</t>
+          <t>34705</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>70056</t>
+          <t>69475</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>103723</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>90667</t>
+          <t>88740</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>131618</t>
+          <t>129153</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>90473</t>
+          <t>90663</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>128792</t>
+          <t>128656</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>193331</t>
+          <t>196032</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>243997</t>
+          <t>245353</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>294889</t>
+          <t>296058</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>359605</t>
+          <t>358337</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>120313</t>
+          <t>120460</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>161219</t>
+          <t>159643</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>199639</t>
+          <t>197443</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>248693</t>
+          <t>249982</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>334427</t>
+          <t>331475</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>400378</t>
+          <t>397373</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>126765</t>
+          <t>125459</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>169169</t>
+          <t>166009</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>149033</t>
+          <t>147065</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>194547</t>
+          <t>193717</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>286688</t>
+          <t>285152</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>347626</t>
+          <t>350522</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>69103</t>
+          <t>69624</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>103122</t>
+          <t>101692</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>40655</t>
+          <t>40575</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>70109</t>
+          <t>71954</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>118634</t>
+          <t>116909</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>164014</t>
+          <t>161288</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8003</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>23609</t>
+          <t>24616</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>103615</t>
+          <t>103162</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>148162</t>
+          <t>147705</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>120062</t>
+          <t>120030</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>167736</t>
+          <t>164539</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>17636</t>
+          <t>17739</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>38089</t>
+          <t>38891</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>264698</t>
+          <t>265378</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>324989</t>
+          <t>323725</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>287416</t>
+          <t>288953</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>349092</t>
+          <t>351054</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>60193</t>
+          <t>59310</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>88495</t>
+          <t>87886</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>327123</t>
+          <t>325769</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>389397</t>
+          <t>388719</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>394651</t>
+          <t>395431</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>466458</t>
+          <t>465167</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>65065</t>
+          <t>66740</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>94455</t>
+          <t>95322</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>175660</t>
+          <t>171224</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>227772</t>
+          <t>223309</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>250826</t>
+          <t>252278</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>309851</t>
+          <t>309572</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>57292</t>
+          <t>55618</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>85204</t>
+          <t>83975</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>105863</t>
+          <t>103080</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>147768</t>
+          <t>149857</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>173121</t>
+          <t>168458</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>223431</t>
+          <t>223744</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>207975</t>
+          <t>208197</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>272484</t>
+          <t>271958</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>353736</t>
+          <t>357751</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>433287</t>
+          <t>435238</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>583044</t>
+          <t>585577</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>682455</t>
+          <t>688152</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>648927</t>
+          <t>650140</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>750619</t>
+          <t>750213</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>903035</t>
+          <t>903789</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1010189</t>
+          <t>1013291</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1582543</t>
+          <t>1576748</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1737171</t>
+          <t>1726285</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>975731</t>
+          <t>977797</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1086088</t>
+          <t>1092500</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1075191</t>
+          <t>1078361</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1190642</t>
+          <t>1191575</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2089381</t>
+          <t>2091517</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2259421</t>
+          <t>2249534</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>876757</t>
+          <t>878404</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>986526</t>
+          <t>978802</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>653664</t>
+          <t>653427</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>756235</t>
+          <t>750827</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1560581</t>
+          <t>1557340</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1707674</t>
+          <t>1703416</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>456034</t>
+          <t>463258</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>547055</t>
+          <t>545813</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>303357</t>
+          <t>302354</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>373381</t>
+          <t>375590</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>782878</t>
+          <t>785726</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>896331</t>
+          <t>893435</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27393</t>
+          <t>28224</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53021</t>
+          <t>54379</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22670</t>
+          <t>21692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44030</t>
+          <t>44242</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56300</t>
+          <t>56034</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87770</t>
+          <t>88892</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56315</t>
+          <t>56265</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88037</t>
+          <t>88343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71110</t>
+          <t>69616</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>102090</t>
+          <t>101940</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>132106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>178411</t>
+          <t>179905</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>178740</t>
+          <t>178715</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>220788</t>
+          <t>221011</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>107005</t>
+          <t>108343</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>143925</t>
+          <t>145723</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>299376</t>
+          <t>299576</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>353843</t>
+          <t>354917</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81536</t>
+          <t>80782</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116750</t>
+          <t>117998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67816</t>
+          <t>67948</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>100430</t>
+          <t>101099</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159076</t>
+          <t>159140</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>208476</t>
+          <t>207287</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31269</t>
+          <t>30094</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28914</t>
+          <t>29148</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27822</t>
+          <t>27155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53775</t>
+          <t>52294</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13974</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34047</t>
+          <t>34147</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16300</t>
+          <t>16471</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37906</t>
+          <t>38752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34683</t>
+          <t>34786</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64156</t>
+          <t>61918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59565</t>
+          <t>60969</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91102</t>
+          <t>93962</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70480</t>
+          <t>68922</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103974</t>
+          <t>105700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139606</t>
+          <t>138014</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>189394</t>
+          <t>183762</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>123975</t>
+          <t>125541</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>163299</t>
+          <t>165199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>134084</t>
+          <t>131604</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>170156</t>
+          <t>169382</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>267822</t>
+          <t>270598</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>322067</t>
+          <t>323314</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86005</t>
+          <t>84711</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122205</t>
+          <t>119327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60076</t>
+          <t>59852</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91893</t>
+          <t>92925</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>153816</t>
+          <t>154643</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>201895</t>
+          <t>202592</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21104</t>
+          <t>21000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42780</t>
+          <t>44526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44737</t>
+          <t>45434</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49262</t>
+          <t>48920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80248</t>
+          <t>79127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>35017</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29461</t>
+          <t>30022</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31530</t>
+          <t>32219</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57513</t>
+          <t>58353</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74331</t>
+          <t>73491</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109885</t>
+          <t>107862</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31819</t>
+          <t>31719</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55714</t>
+          <t>56361</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111588</t>
+          <t>111648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>154059</t>
+          <t>154536</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195866</t>
+          <t>194391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>242232</t>
+          <t>242514</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40032</t>
+          <t>41215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65800</t>
+          <t>66599</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>243351</t>
+          <t>243940</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>297490</t>
+          <t>295661</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110566</t>
+          <t>111050</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>152141</t>
+          <t>153032</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31426</t>
+          <t>31025</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54246</t>
+          <t>54969</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>150350</t>
+          <t>148797</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>194237</t>
+          <t>194241</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45545</t>
+          <t>45107</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74254</t>
+          <t>74658</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16577</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54153</t>
+          <t>53714</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86908</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55528</t>
+          <t>55079</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88912</t>
+          <t>86726</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54519</t>
+          <t>52847</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86024</t>
+          <t>84961</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119690</t>
+          <t>117315</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>165056</t>
+          <t>163361</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>147845</t>
+          <t>151297</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>199758</t>
+          <t>201514</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136644</t>
+          <t>136568</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>181730</t>
+          <t>180317</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>298361</t>
+          <t>297452</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>364153</t>
+          <t>365383</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>388043</t>
+          <t>389948</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>455143</t>
+          <t>455797</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>294522</t>
+          <t>295320</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>351055</t>
+          <t>351597</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>699130</t>
+          <t>701440</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>785003</t>
+          <t>784975</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>305332</t>
+          <t>301195</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>368599</t>
+          <t>364787</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>177366</t>
+          <t>176871</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>224322</t>
+          <t>225082</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>495251</t>
+          <t>491991</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>574042</t>
+          <t>573351</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123215</t>
+          <t>123079</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>171927</t>
+          <t>168469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58394</t>
+          <t>58656</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>93549</t>
+          <t>91396</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>191436</t>
+          <t>191135</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>247192</t>
+          <t>246290</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36351</t>
+          <t>36524</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>64769</t>
+          <t>64424</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>48001</t>
+          <t>48048</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80289</t>
+          <t>78508</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>91374</t>
+          <t>92171</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>132182</t>
+          <t>136829</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>93070</t>
+          <t>92204</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>131865</t>
+          <t>129155</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>147940</t>
+          <t>145894</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>194166</t>
+          <t>191421</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>251115</t>
+          <t>250519</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>309926</t>
+          <t>310169</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>198463</t>
+          <t>199459</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>245941</t>
+          <t>247321</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>265060</t>
+          <t>262566</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>319580</t>
+          <t>316861</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>478602</t>
+          <t>481621</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>548741</t>
+          <t>551727</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>132092</t>
+          <t>134247</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>177426</t>
+          <t>178763</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>141361</t>
+          <t>140832</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>187497</t>
+          <t>186260</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>285614</t>
+          <t>287084</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>348803</t>
+          <t>351595</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>65413</t>
+          <t>65506</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>99552</t>
+          <t>98559</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>36543</t>
+          <t>37997</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>64913</t>
+          <t>65254</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>112093</t>
+          <t>111179</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>155319</t>
+          <t>155653</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>23352</t>
+          <t>21577</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>94653</t>
+          <t>92761</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>133342</t>
+          <t>134566</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>106474</t>
+          <t>105908</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>149477</t>
+          <t>152156</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23254</t>
+          <t>23944</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>45259</t>
+          <t>47068</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>221661</t>
+          <t>224555</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>280776</t>
+          <t>281661</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>256266</t>
+          <t>253422</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>320648</t>
+          <t>316159</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>83826</t>
+          <t>84825</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>117427</t>
+          <t>116198</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>360532</t>
+          <t>354832</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>421085</t>
+          <t>420376</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>450825</t>
+          <t>451871</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>522839</t>
+          <t>522228</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>84406</t>
+          <t>83708</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>117098</t>
+          <t>115187</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>221704</t>
+          <t>218762</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>278458</t>
+          <t>277145</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>318892</t>
+          <t>314554</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>384621</t>
+          <t>378655</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>30439</t>
+          <t>31724</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>55012</t>
+          <t>54446</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>61012</t>
+          <t>61227</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>95277</t>
+          <t>94739</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>99518</t>
+          <t>96338</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>141655</t>
+          <t>139394</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>189538</t>
+          <t>187989</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>249118</t>
+          <t>246887</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>287188</t>
+          <t>286223</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>358390</t>
+          <t>355739</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>497742</t>
+          <t>491991</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>587928</t>
+          <t>587850</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>510911</t>
+          <t>509951</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>601161</t>
+          <t>598112</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>742395</t>
+          <t>743547</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>843877</t>
+          <t>841783</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1275266</t>
+          <t>1283285</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1414937</t>
+          <t>1414876</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1245251</t>
+          <t>1248175</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1359887</t>
+          <t>1365504</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1273591</t>
+          <t>1276017</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1387385</t>
+          <t>1395249</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2557248</t>
+          <t>2557221</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2718690</t>
+          <t>2718169</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>870015</t>
+          <t>869589</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>971240</t>
+          <t>976102</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>764120</t>
+          <t>759451</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>862645</t>
+          <t>864371</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1663646</t>
+          <t>1663575</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1808147</t>
+          <t>1808628</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>338861</t>
+          <t>341039</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>416924</t>
+          <t>416911</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>227381</t>
+          <t>232789</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>293944</t>
+          <t>292870</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>587704</t>
+          <t>592543</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>686528</t>
+          <t>688607</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
